--- a/docs/new-engine-example.xlsx
+++ b/docs/new-engine-example.xlsx
@@ -3141,7 +3141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AK17"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3170,6 +3170,16 @@
     <col min="25" max="25" width="20.83203125" customWidth="1"/>
     <col min="26" max="26" width="20.83203125" customWidth="1"/>
     <col min="27" max="27" width="20.83203125" customWidth="1"/>
+    <col min="28" max="28" width="20.83203125" customWidth="1"/>
+    <col min="29" max="29" width="20.83203125" customWidth="1"/>
+    <col min="30" max="30" width="20.83203125" customWidth="1"/>
+    <col min="31" max="31" width="20.83203125" customWidth="1"/>
+    <col min="32" max="32" width="20.83203125" customWidth="1"/>
+    <col min="33" max="33" width="20.83203125" customWidth="1"/>
+    <col min="34" max="34" width="20.83203125" customWidth="1"/>
+    <col min="35" max="35" width="20.83203125" customWidth="1"/>
+    <col min="36" max="36" width="20.83203125" customWidth="1"/>
+    <col min="37" max="37" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3216,42 +3226,72 @@
         <v>条件2值2</v>
       </c>
       <c r="O1" t="str">
+        <v>条件3字段</v>
+      </c>
+      <c r="P1" t="str">
+        <v>条件3运算符</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>条件3值</v>
+      </c>
+      <c r="R1" t="str">
+        <v>条件3值2</v>
+      </c>
+      <c r="S1" t="str">
+        <v>条件4字段</v>
+      </c>
+      <c r="T1" t="str">
+        <v>条件4运算符</v>
+      </c>
+      <c r="U1" t="str">
+        <v>条件4值</v>
+      </c>
+      <c r="V1" t="str">
+        <v>条件4值2</v>
+      </c>
+      <c r="W1" t="str">
+        <v>条件结构</v>
+      </c>
+      <c r="X1" t="str">
+        <v>条件数据</v>
+      </c>
+      <c r="Y1" t="str">
         <v>计算方式</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Z1" t="str">
         <v>查表名称</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="AA1" t="str">
         <v>匹配方式</v>
       </c>
-      <c r="R1" t="str">
+      <c r="AB1" t="str">
         <v>输入映射</v>
       </c>
-      <c r="S1" t="str">
+      <c r="AC1" t="str">
         <v>输出列</v>
       </c>
-      <c r="T1" t="str">
+      <c r="AD1" t="str">
         <v>百分比基数</v>
       </c>
-      <c r="U1" t="str">
+      <c r="AE1" t="str">
         <v>百分比值</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AF1" t="str">
         <v>百分比来源字段</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AG1" t="str">
         <v>固定金额</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AH1" t="str">
         <v>加总字段</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AI1" t="str">
         <v>公式</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AJ1" t="str">
         <v>累加</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AK1" t="str">
         <v>说明</v>
       </c>
     </row>
@@ -3299,42 +3339,72 @@
         <v/>
       </c>
       <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
         <v>查表</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Z2" t="str">
         <v>commission_table</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="AA2" t="str">
         <v>精确</v>
       </c>
-      <c r="R2" t="str">
+      <c r="AB2" t="str">
         <v>刊登类型=刊登类型,商品类目=类目</v>
       </c>
-      <c r="S2" t="str">
+      <c r="AC2" t="str">
         <v>费率</v>
       </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
         <v>否</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AK2" t="str">
         <v>按刊登类型+类目查佣金费率表</v>
       </c>
     </row>
@@ -3382,42 +3452,72 @@
         <v/>
       </c>
       <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
         <v>百分比</v>
       </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
         <v>售价</v>
       </c>
-      <c r="U3" t="str">
-        <v/>
-      </c>
-      <c r="V3" t="str">
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
         <v>销售佣金费率</v>
       </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
         <v>否</v>
       </c>
-      <c r="AA3" t="str">
+      <c r="AK3" t="str">
         <v>售价 × 上一步查出的佣金费率</v>
       </c>
     </row>
@@ -3465,42 +3565,72 @@
         <v/>
       </c>
       <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
         <v>固定值</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <v/>
-      </c>
-      <c r="W4" t="str">
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
         <v>0</v>
       </c>
-      <c r="X4" t="str">
-        <v/>
-      </c>
-      <c r="Y4" t="str">
-        <v/>
-      </c>
-      <c r="Z4" t="str">
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
         <v>否</v>
       </c>
-      <c r="AA4" t="str">
+      <c r="AK4" t="str">
         <v>包邮免费，不产生运费</v>
       </c>
     </row>
@@ -3548,42 +3678,72 @@
         <v/>
       </c>
       <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
         <v>查表</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Z5" t="str">
         <v>shipping_table</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="AA5" t="str">
         <v>区间</v>
       </c>
-      <c r="R5" t="str">
+      <c r="AB5" t="str">
         <v>售价=范围1,重量=范围2</v>
       </c>
-      <c r="S5" t="str">
+      <c r="AC5" t="str">
         <v>运费</v>
       </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
-        <v/>
-      </c>
-      <c r="Y5" t="str">
-        <v/>
-      </c>
-      <c r="Z5" t="str">
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
         <v>否</v>
       </c>
-      <c r="AA5" t="str">
+      <c r="AK5" t="str">
         <v>不包邮时按售价区间+重量区间查运费表。区间左闭右闭，按表顺序取第一条匹配</v>
       </c>
     </row>
@@ -3631,42 +3791,72 @@
         <v/>
       </c>
       <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
         <v>百分比</v>
       </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v/>
+      </c>
+      <c r="AD6" t="str">
         <v>售价</v>
       </c>
-      <c r="U6" t="str">
+      <c r="AE6" t="str">
         <v>4.8</v>
       </c>
-      <c r="V6" t="str">
-        <v/>
-      </c>
-      <c r="W6" t="str">
-        <v/>
-      </c>
-      <c r="X6" t="str">
-        <v/>
-      </c>
-      <c r="Y6" t="str">
-        <v/>
-      </c>
-      <c r="Z6" t="str">
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
         <v>否</v>
       </c>
-      <c r="AA6" t="str">
+      <c r="AK6" t="str">
         <v>ML支付系统手续费，售价的 4.8%</v>
       </c>
     </row>
@@ -3714,42 +3904,72 @@
         <v/>
       </c>
       <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
         <v>加总</v>
       </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-      <c r="U7" t="str">
-        <v/>
-      </c>
-      <c r="V7" t="str">
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <v/>
-      </c>
-      <c r="X7" t="str">
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
         <v>销售佣金金额,运费,支付手续费</v>
       </c>
-      <c r="Y7" t="str">
-        <v/>
-      </c>
-      <c r="Z7" t="str">
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
         <v>否</v>
       </c>
-      <c r="AA7" t="str">
+      <c r="AK7" t="str">
         <v>累加所有费用项</v>
       </c>
     </row>
@@ -3797,42 +4017,72 @@
         <v/>
       </c>
       <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
         <v>公式</v>
       </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-      <c r="U8" t="str">
-        <v/>
-      </c>
-      <c r="V8" t="str">
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <v/>
-      </c>
-      <c r="X8" t="str">
-        <v/>
-      </c>
-      <c r="Y8" t="str">
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v/>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
         <v>售价 - 总费用 - 成本价</v>
       </c>
-      <c r="Z8" t="str">
+      <c r="AJ8" t="str">
         <v>否</v>
       </c>
-      <c r="AA8" t="str">
+      <c r="AK8" t="str">
         <v>净利润 = 售价 − 总费用 − 成本价</v>
       </c>
     </row>
@@ -3880,42 +4130,72 @@
         <v/>
       </c>
       <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
         <v>公式</v>
       </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-      <c r="U9" t="str">
-        <v/>
-      </c>
-      <c r="V9" t="str">
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <v/>
-      </c>
-      <c r="X9" t="str">
-        <v/>
-      </c>
-      <c r="Y9" t="str">
+      <c r="Z9" t="str">
+        <v/>
+      </c>
+      <c r="AA9" t="str">
+        <v/>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v/>
+      </c>
+      <c r="AI9" t="str">
         <v>净利润 / 售价</v>
       </c>
-      <c r="Z9" t="str">
+      <c r="AJ9" t="str">
         <v>否</v>
       </c>
-      <c r="AA9" t="str">
+      <c r="AK9" t="str">
         <v>利润率 = 净利润 ÷ 售价</v>
       </c>
     </row>
@@ -3963,42 +4243,72 @@
         <v/>
       </c>
       <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
         <v>查表</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Z10" t="str">
         <v>commission_table_mx</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="AA10" t="str">
         <v>精确</v>
       </c>
-      <c r="R10" t="str">
+      <c r="AB10" t="str">
         <v>刊登类型=刊登类型,商品类目=类目</v>
       </c>
-      <c r="S10" t="str">
+      <c r="AC10" t="str">
         <v>费率</v>
       </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <v/>
-      </c>
-      <c r="X10" t="str">
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <v/>
-      </c>
-      <c r="Z10" t="str">
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
+        <v/>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v/>
+      </c>
+      <c r="AI10" t="str">
+        <v/>
+      </c>
+      <c r="AJ10" t="str">
         <v>否</v>
       </c>
-      <c r="AA10" t="str">
+      <c r="AK10" t="str">
         <v>墨西哥站佣金查表</v>
       </c>
     </row>
@@ -4046,42 +4356,72 @@
         <v/>
       </c>
       <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
         <v>百分比</v>
       </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
+      <c r="Z11" t="str">
+        <v/>
+      </c>
+      <c r="AA11" t="str">
+        <v/>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v/>
+      </c>
+      <c r="AD11" t="str">
         <v>售价</v>
       </c>
-      <c r="U11" t="str">
-        <v/>
-      </c>
-      <c r="V11" t="str">
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
         <v>销售佣金费率</v>
       </c>
-      <c r="W11" t="str">
-        <v/>
-      </c>
-      <c r="X11" t="str">
-        <v/>
-      </c>
-      <c r="Y11" t="str">
-        <v/>
-      </c>
-      <c r="Z11" t="str">
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v/>
+      </c>
+      <c r="AI11" t="str">
+        <v/>
+      </c>
+      <c r="AJ11" t="str">
         <v>否</v>
       </c>
-      <c r="AA11" t="str">
+      <c r="AK11" t="str">
         <v>售价 × 佣金费率</v>
       </c>
     </row>
@@ -4129,42 +4469,72 @@
         <v/>
       </c>
       <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
         <v>固定值</v>
       </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v/>
-      </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
-      <c r="U12" t="str">
-        <v/>
-      </c>
-      <c r="V12" t="str">
-        <v/>
-      </c>
-      <c r="W12" t="str">
+      <c r="Z12" t="str">
+        <v/>
+      </c>
+      <c r="AA12" t="str">
+        <v/>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <v/>
+      </c>
+      <c r="AG12" t="str">
         <v>0</v>
       </c>
-      <c r="X12" t="str">
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <v/>
-      </c>
-      <c r="Z12" t="str">
+      <c r="AH12" t="str">
+        <v/>
+      </c>
+      <c r="AI12" t="str">
+        <v/>
+      </c>
+      <c r="AJ12" t="str">
         <v>否</v>
       </c>
-      <c r="AA12" t="str">
+      <c r="AK12" t="str">
         <v>包邮免费</v>
       </c>
     </row>
@@ -4212,42 +4582,72 @@
         <v/>
       </c>
       <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
         <v>查表</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Z13" t="str">
         <v>shipping_table_mx</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="AA13" t="str">
         <v>区间</v>
       </c>
-      <c r="R13" t="str">
+      <c r="AB13" t="str">
         <v>售价=范围1,重量=范围2</v>
       </c>
-      <c r="S13" t="str">
+      <c r="AC13" t="str">
         <v>运费</v>
       </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-      <c r="U13" t="str">
-        <v/>
-      </c>
-      <c r="V13" t="str">
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <v/>
-      </c>
-      <c r="X13" t="str">
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <v/>
-      </c>
-      <c r="Z13" t="str">
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <v/>
+      </c>
+      <c r="AI13" t="str">
+        <v/>
+      </c>
+      <c r="AJ13" t="str">
         <v>否</v>
       </c>
-      <c r="AA13" t="str">
+      <c r="AK13" t="str">
         <v>不包邮时查墨西哥运费表</v>
       </c>
     </row>
@@ -4295,42 +4695,72 @@
         <v/>
       </c>
       <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
         <v>百分比</v>
       </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
+      <c r="Z14" t="str">
+        <v/>
+      </c>
+      <c r="AA14" t="str">
+        <v/>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v/>
+      </c>
+      <c r="AD14" t="str">
         <v>售价</v>
       </c>
-      <c r="U14" t="str">
+      <c r="AE14" t="str">
         <v>3.5</v>
       </c>
-      <c r="V14" t="str">
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <v/>
-      </c>
-      <c r="Z14" t="str">
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v/>
+      </c>
+      <c r="AI14" t="str">
+        <v/>
+      </c>
+      <c r="AJ14" t="str">
         <v>否</v>
       </c>
-      <c r="AA14" t="str">
+      <c r="AK14" t="str">
         <v>墨西哥支付手续费 3.5%</v>
       </c>
     </row>
@@ -4378,42 +4808,72 @@
         <v/>
       </c>
       <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
         <v>加总</v>
       </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
+      <c r="Z15" t="str">
+        <v/>
+      </c>
+      <c r="AA15" t="str">
+        <v/>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
         <v>销售佣金金额,运费,支付手续费</v>
       </c>
-      <c r="Y15" t="str">
-        <v/>
-      </c>
-      <c r="Z15" t="str">
+      <c r="AI15" t="str">
+        <v/>
+      </c>
+      <c r="AJ15" t="str">
         <v>否</v>
       </c>
-      <c r="AA15" t="str">
+      <c r="AK15" t="str">
         <v>累加所有费用</v>
       </c>
     </row>
@@ -4461,42 +4921,72 @@
         <v/>
       </c>
       <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
         <v>公式</v>
       </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str">
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <v/>
-      </c>
-      <c r="X16" t="str">
-        <v/>
-      </c>
-      <c r="Y16" t="str">
+      <c r="Z16" t="str">
+        <v/>
+      </c>
+      <c r="AA16" t="str">
+        <v/>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v/>
+      </c>
+      <c r="AI16" t="str">
         <v>售价 - 总费用 - 成本价</v>
       </c>
-      <c r="Z16" t="str">
+      <c r="AJ16" t="str">
         <v>否</v>
       </c>
-      <c r="AA16" t="str">
+      <c r="AK16" t="str">
         <v>净利润</v>
       </c>
     </row>
@@ -4544,48 +5034,78 @@
         <v/>
       </c>
       <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
         <v>公式</v>
       </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-      <c r="U17" t="str">
-        <v/>
-      </c>
-      <c r="V17" t="str">
-        <v/>
-      </c>
-      <c r="W17" t="str">
-        <v/>
-      </c>
-      <c r="X17" t="str">
-        <v/>
-      </c>
-      <c r="Y17" t="str">
+      <c r="Z17" t="str">
+        <v/>
+      </c>
+      <c r="AA17" t="str">
+        <v/>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v/>
+      </c>
+      <c r="AI17" t="str">
         <v>净利润 / 售价</v>
       </c>
-      <c r="Z17" t="str">
+      <c r="AJ17" t="str">
         <v>否</v>
       </c>
-      <c r="AA17" t="str">
+      <c r="AK17" t="str">
         <v>利润率</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AK17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/new-engine-example.xlsx
+++ b/docs/new-engine-example.xlsx
@@ -415,13 +415,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>平台</v>
+      </c>
+      <c r="B1" t="str">
         <v>国家</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>编号</v>
-      </c>
-      <c r="C1" t="str">
-        <v>平台</v>
       </c>
       <c r="D1" t="str">
         <v>货币</v>
@@ -444,13 +444,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="B2" t="str">
         <v>巴西</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>cp_br</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Mercado Livre</v>
       </c>
       <c r="D2" t="str">
         <v>BRL</v>
@@ -473,13 +473,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="B3" t="str">
         <v>墨西哥</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>cp_mx</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Mercado Livre</v>
       </c>
       <c r="D3" t="str">
         <v>MXN</v>
@@ -502,13 +502,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Mercado Livre</v>
+      </c>
+      <c r="B4" t="str">
         <v>阿根廷</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>cp_ar</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Mercado Livre</v>
       </c>
       <c r="D4" t="str">
         <v>ARS</v>
@@ -6453,44 +6453,44 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>br_刊登类型</v>
+        <v>br_布尔</v>
       </c>
       <c r="B5" t="str">
-        <v>刊登类型</v>
+        <v>是/否</v>
       </c>
       <c r="C5" t="str">
         <v>cp_br</v>
       </c>
       <c r="D5" t="str">
-        <v>ML巴西站刊登方式</v>
+        <v>通用布尔选项</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>br_商品类目</v>
+        <v>br_刊登类型</v>
       </c>
       <c r="B6" t="str">
-        <v>商品类目</v>
+        <v>刊登类型</v>
       </c>
       <c r="C6" t="str">
         <v>cp_br</v>
       </c>
       <c r="D6" t="str">
-        <v>ML巴西站商品一级类目</v>
+        <v>ML巴西站刊登方式</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>br_布尔</v>
+        <v>br_商品类目</v>
       </c>
       <c r="B7" t="str">
-        <v>是/否</v>
+        <v>商品类目</v>
       </c>
       <c r="C7" t="str">
         <v>cp_br</v>
       </c>
       <c r="D7" t="str">
-        <v>通用布尔选项</v>
+        <v>ML巴西站商品一级类目</v>
       </c>
     </row>
   </sheetData>

--- a/docs/new-engine-example.xlsx
+++ b/docs/new-engine-example.xlsx
@@ -23,15 +23,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="540">
   <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
     <t>平台</t>
   </si>
   <si>
-    <t>国家</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
     <t>货币</t>
   </si>
   <si>
@@ -50,15 +50,15 @@
     <t>备注</t>
   </si>
   <si>
+    <t>cp_br</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
     <t>Mercado Livre</t>
   </si>
   <si>
-    <t>巴西</t>
-  </si>
-  <si>
-    <t>cp_br</t>
-  </si>
-  <si>
     <t>BRL</t>
   </si>
   <si>
@@ -77,12 +77,12 @@
     <t>巴西ML站，主要运营站点</t>
   </si>
   <si>
+    <t>cp_mx</t>
+  </si>
+  <si>
     <t>墨西哥</t>
   </si>
   <si>
-    <t>cp_mx</t>
-  </si>
-  <si>
     <t>MXN</t>
   </si>
   <si>
@@ -98,10 +98,10 @@
     <t>墨西哥ML站，2026年计划拓展</t>
   </si>
   <si>
+    <t>cp_ar</t>
+  </si>
+  <si>
     <t>阿根廷</t>
-  </si>
-  <si>
-    <t>cp_ar</t>
   </si>
   <si>
     <t>ARS</t>
@@ -2030,8 +2030,9 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="4" width="8" customWidth="1"/>
+    <col min="1" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
@@ -2097,13 +2098,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>20</v>
@@ -2126,13 +2127,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>27</v>
@@ -7101,7 +7102,7 @@
         <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>48</v>
@@ -7136,7 +7137,7 @@
         <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>48</v>
@@ -7171,7 +7172,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>48</v>
@@ -7206,7 +7207,7 @@
         <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>56</v>
@@ -7241,7 +7242,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>56</v>
@@ -7276,7 +7277,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>56</v>
@@ -7311,7 +7312,7 @@
         <v>46</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>56</v>
@@ -7346,7 +7347,7 @@
         <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>56</v>
@@ -7381,7 +7382,7 @@
         <v>46</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>56</v>
@@ -7416,7 +7417,7 @@
         <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>56</v>
@@ -7451,7 +7452,7 @@
         <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>56</v>
@@ -7486,7 +7487,7 @@
         <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>56</v>
@@ -7521,7 +7522,7 @@
         <v>46</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>56</v>
@@ -7556,7 +7557,7 @@
         <v>69</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>48</v>
@@ -7591,7 +7592,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>48</v>
@@ -7626,7 +7627,7 @@
         <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>48</v>
@@ -7661,7 +7662,7 @@
         <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>56</v>
@@ -7696,7 +7697,7 @@
         <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>56</v>
@@ -7731,7 +7732,7 @@
         <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>56</v>
@@ -7766,7 +7767,7 @@
         <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>48</v>
@@ -7801,7 +7802,7 @@
         <v>46</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>56</v>
@@ -7836,7 +7837,7 @@
         <v>46</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>56</v>
@@ -7871,7 +7872,7 @@
         <v>46</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>56</v>
@@ -7906,7 +7907,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>56</v>
@@ -7941,7 +7942,7 @@
         <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>56</v>
@@ -7976,7 +7977,7 @@
         <v>46</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>56</v>
@@ -8011,7 +8012,7 @@
         <v>46</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>56</v>
@@ -8048,7 +8049,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>89</v>
@@ -8068,7 +8069,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>90</v>
@@ -8082,7 +8083,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>91</v>
@@ -8096,7 +8097,7 @@
         <v>92</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>93</v>
@@ -8110,7 +8111,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>94</v>
@@ -8124,7 +8125,7 @@
         <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>93</v>
@@ -8138,7 +8139,7 @@
         <v>50</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>95</v>
@@ -8688,7 +8689,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>89</v>
@@ -8711,7 +8712,7 @@
         <v>123</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -8728,7 +8729,7 @@
         <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>15</v>
@@ -8783,7 +8784,7 @@
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>128</v>

--- a/docs/new-engine-example.xlsx
+++ b/docs/new-engine-example.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="540">
   <si>
     <t>编号</t>
   </si>
@@ -44,331 +44,331 @@
     <t>启用</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>cp_br</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>R$</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>巴西ML站，主要运营站点</t>
+  </si>
+  <si>
+    <t>cp_mx</t>
+  </si>
+  <si>
+    <t>墨西哥</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t>MX$</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>墨西哥ML站，2026年计划拓展</t>
+  </si>
+  <si>
+    <t>cp_ar</t>
+  </si>
+  <si>
+    <t>阿根廷</t>
+  </si>
+  <si>
+    <t>ARS</t>
+  </si>
+  <si>
+    <t>AR$</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>阿根廷站点，汇率不稳定暂缓</t>
+  </si>
+  <si>
+    <t>字段键</t>
+  </si>
+  <si>
+    <t>字段名称</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>选项组编号</t>
+  </si>
+  <si>
+    <t>所属国家平台</t>
+  </si>
+  <si>
+    <t>层级</t>
+  </si>
+  <si>
+    <t>输入输出</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>默认值</t>
+  </si>
+  <si>
+    <t>刊登类型</t>
+  </si>
+  <si>
+    <t>下拉</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>mx_刊登类型</t>
+  </si>
+  <si>
+    <t>商品级</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>商品类目</t>
+  </si>
+  <si>
+    <t>mx_商品类目</t>
+  </si>
+  <si>
+    <t>是否包邮</t>
+  </si>
+  <si>
+    <t>mx_布尔</t>
+  </si>
+  <si>
+    <t>售价</t>
+  </si>
+  <si>
+    <t>数字</t>
+  </si>
+  <si>
+    <t>SKU级</t>
+  </si>
+  <si>
+    <t>成本价</t>
+  </si>
+  <si>
+    <t>重量</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>销售佣金费率</t>
+  </si>
+  <si>
+    <t>输出</t>
+  </si>
+  <si>
+    <t>销售佣金金额</t>
+  </si>
+  <si>
+    <t>运费</t>
+  </si>
+  <si>
+    <t>支付手续费</t>
+  </si>
+  <si>
+    <t>总费用</t>
+  </si>
+  <si>
+    <t>净利润</t>
+  </si>
+  <si>
+    <t>利润率</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>br_商品类目</t>
+  </si>
+  <si>
+    <t>美容、个护、家居等</t>
+  </si>
+  <si>
+    <t>美容</t>
+  </si>
+  <si>
+    <t>br_刊登类型</t>
+  </si>
+  <si>
+    <t>Classico / Premium</t>
+  </si>
+  <si>
+    <t>br_布尔</t>
+  </si>
+  <si>
+    <t>是=卖家包邮 / 否=买家付运费</t>
+  </si>
+  <si>
+    <t>商品售价，每个变体可不同</t>
+  </si>
+  <si>
+    <t>采购成本+头程运费</t>
+  </si>
+  <si>
+    <t>商品重量，每个变体可不同</t>
+  </si>
+  <si>
+    <t>装箱数量</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>每箱商品数量</t>
+  </si>
+  <si>
+    <t>系统计算：查表得到的佣金费率</t>
+  </si>
+  <si>
+    <t>系统计算：售价 × 佣金费率</t>
+  </si>
+  <si>
+    <t>系统计算：运费</t>
+  </si>
+  <si>
+    <t>系统计算：售价 × 4.8%</t>
+  </si>
+  <si>
+    <t>系统计算：佣金 + 运费 + 手续费</t>
+  </si>
+  <si>
+    <t>售价 − 总费用 − 成本价</t>
+  </si>
+  <si>
+    <t>净利润 ÷ 售价</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>ML墨西哥站刊登方式</t>
+  </si>
+  <si>
+    <t>ML墨西哥站商品一级类目</t>
+  </si>
+  <si>
+    <t>是/否</t>
+  </si>
+  <si>
+    <t>通用布尔选项</t>
+  </si>
+  <si>
+    <t>ML巴西站刊登方式</t>
+  </si>
+  <si>
+    <t>ML巴西站商品一级类目</t>
+  </si>
+  <si>
+    <t>所属分组</t>
+  </si>
+  <si>
+    <t>选项值</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
     <t>排序</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>cp_br</t>
-  </si>
-  <si>
-    <t>巴西</t>
-  </si>
-  <si>
-    <t>Mercado Livre</t>
-  </si>
-  <si>
-    <t>BRL</t>
-  </si>
-  <si>
-    <t>R$</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>是</t>
+    <t>_uid</t>
+  </si>
+  <si>
+    <t>classico</t>
+  </si>
+  <si>
+    <t>Classico 经典</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>巴西ML站，主要运营站点</t>
-  </si>
-  <si>
-    <t>cp_mx</t>
-  </si>
-  <si>
-    <t>墨西哥</t>
-  </si>
-  <si>
-    <t>MXN</t>
-  </si>
-  <si>
-    <t>MX$</t>
-  </si>
-  <si>
-    <t>0.42</t>
+    <t>premium</t>
+  </si>
+  <si>
+    <t>Premium 高级</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>墨西哥ML站，2026年计划拓展</t>
-  </si>
-  <si>
-    <t>cp_ar</t>
-  </si>
-  <si>
-    <t>阿根廷</t>
-  </si>
-  <si>
-    <t>ARS</t>
-  </si>
-  <si>
-    <t>AR$</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>否</t>
+    <t>beauty</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>家居</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>未分类商品</t>
+  </si>
+  <si>
+    <t>广告</t>
+  </si>
+  <si>
+    <t>广告 1</t>
+  </si>
+  <si>
+    <t>广告2</t>
+  </si>
+  <si>
+    <t>广告 2</t>
+  </si>
+  <si>
+    <t>个护</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>阿根廷站点，汇率不稳定暂缓</t>
-  </si>
-  <si>
-    <t>字段键</t>
-  </si>
-  <si>
-    <t>字段名称</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>选项组编号</t>
-  </si>
-  <si>
-    <t>所属国家平台</t>
-  </si>
-  <si>
-    <t>层级</t>
-  </si>
-  <si>
-    <t>输入输出</t>
-  </si>
-  <si>
-    <t>必填</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>默认值</t>
-  </si>
-  <si>
-    <t>刊登类型</t>
-  </si>
-  <si>
-    <t>下拉</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>mx_刊登类型</t>
-  </si>
-  <si>
-    <t>商品级</t>
-  </si>
-  <si>
-    <t>输入</t>
-  </si>
-  <si>
-    <t>商品类目</t>
-  </si>
-  <si>
-    <t>mx_商品类目</t>
-  </si>
-  <si>
-    <t>是否包邮</t>
-  </si>
-  <si>
-    <t>mx_布尔</t>
-  </si>
-  <si>
-    <t>售价</t>
-  </si>
-  <si>
-    <t>数字</t>
-  </si>
-  <si>
-    <t>SKU级</t>
-  </si>
-  <si>
-    <t>成本价</t>
-  </si>
-  <si>
-    <t>重量</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>销售佣金费率</t>
-  </si>
-  <si>
-    <t>输出</t>
-  </si>
-  <si>
-    <t>销售佣金金额</t>
-  </si>
-  <si>
-    <t>运费</t>
-  </si>
-  <si>
-    <t>支付手续费</t>
-  </si>
-  <si>
-    <t>总费用</t>
-  </si>
-  <si>
-    <t>净利润</t>
-  </si>
-  <si>
-    <t>利润率</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>br_商品类目</t>
-  </si>
-  <si>
-    <t>美容、个护、家居等</t>
-  </si>
-  <si>
-    <t>美容</t>
-  </si>
-  <si>
-    <t>br_刊登类型</t>
-  </si>
-  <si>
-    <t>Classico / Premium</t>
-  </si>
-  <si>
-    <t>br_布尔</t>
-  </si>
-  <si>
-    <t>是=卖家包邮 / 否=买家付运费</t>
-  </si>
-  <si>
-    <t>商品售价，每个变体可不同</t>
-  </si>
-  <si>
-    <t>采购成本+头程运费</t>
-  </si>
-  <si>
-    <t>商品重量，每个变体可不同</t>
-  </si>
-  <si>
-    <t>装箱数量</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>每箱商品数量</t>
-  </si>
-  <si>
-    <t>系统计算：查表得到的佣金费率</t>
-  </si>
-  <si>
-    <t>系统计算：售价 × 佣金费率</t>
-  </si>
-  <si>
-    <t>系统计算：运费</t>
-  </si>
-  <si>
-    <t>系统计算：售价 × 4.8%</t>
-  </si>
-  <si>
-    <t>系统计算：佣金 + 运费 + 手续费</t>
-  </si>
-  <si>
-    <t>售价 − 总费用 − 成本价</t>
-  </si>
-  <si>
-    <t>净利润 ÷ 售价</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>ML墨西哥站刊登方式</t>
-  </si>
-  <si>
-    <t>ML墨西哥站商品一级类目</t>
-  </si>
-  <si>
-    <t>是/否</t>
-  </si>
-  <si>
-    <t>通用布尔选项</t>
-  </si>
-  <si>
-    <t>ML巴西站刊登方式</t>
-  </si>
-  <si>
-    <t>ML巴西站商品一级类目</t>
-  </si>
-  <si>
-    <t>所属分组</t>
-  </si>
-  <si>
-    <t>选项值</t>
-  </si>
-  <si>
-    <t>显示名</t>
-  </si>
-  <si>
-    <t>_uid</t>
-  </si>
-  <si>
-    <t>classico</t>
-  </si>
-  <si>
-    <t>Classico 经典</t>
-  </si>
-  <si>
-    <t>premium</t>
-  </si>
-  <si>
-    <t>Premium 高级</t>
-  </si>
-  <si>
-    <t>beauty</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>家居</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>未分类商品</t>
-  </si>
-  <si>
-    <t>广告</t>
-  </si>
-  <si>
-    <t>广告 1</t>
-  </si>
-  <si>
-    <t>广告2</t>
-  </si>
-  <si>
-    <t>广告 2</t>
-  </si>
-  <si>
-    <t>个护</t>
   </si>
   <si>
     <t>电子产品</t>
@@ -2027,18 +2027,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="6" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2063,95 +2063,83 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2172,7 +2160,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>226</v>
@@ -2181,15 +2169,15 @@
         <v>168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>291</v>
@@ -2200,10 +2188,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>293</v>
@@ -2214,10 +2202,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>235</v>
@@ -2228,10 +2216,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>237</v>
@@ -2242,10 +2230,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>227</v>
@@ -2256,10 +2244,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>229</v>
@@ -2270,7 +2258,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>299</v>
@@ -2284,7 +2272,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>299</v>
@@ -2298,7 +2286,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>118</v>
@@ -2312,7 +2300,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>118</v>
@@ -2326,10 +2314,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>304</v>
@@ -2340,10 +2328,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>306</v>
@@ -2382,10 +2370,10 @@
         <v>242</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7052,982 +7040,982 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8052,97 +8040,97 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -8166,352 +8154,352 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>116</v>
@@ -8523,18 +8511,18 @@
         <v>117</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>118</v>
@@ -8546,56 +8534,56 @@
         <v>119</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -8603,22 +8591,22 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -8626,19 +8614,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>120</v>
@@ -8649,19 +8637,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D22" s="3">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>121</v>
@@ -8692,16 +8680,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8712,10 +8700,10 @@
         <v>123</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>124</v>
@@ -8729,10 +8717,10 @@
         <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>127</v>
@@ -8892,7 +8880,7 @@
         <v>161</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
@@ -8903,70 +8891,70 @@
         <v>125</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>164</v>
@@ -8984,25 +8972,25 @@
         <v>168</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK2" s="3" t="s">
         <v>169</v>
@@ -9016,106 +9004,106 @@
         <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>172</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK3" s="3" t="s">
         <v>173</v>
@@ -9129,106 +9117,106 @@
         <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>175</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>176</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>177</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG4" s="3" t="s">
         <v>178</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>179</v>
@@ -9242,70 +9230,70 @@
         <v>125</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>181</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>182</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>164</v>
@@ -9320,28 +9308,28 @@
         <v>185</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK5" s="3" t="s">
         <v>186</v>
@@ -9355,106 +9343,106 @@
         <v>125</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>188</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>172</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD6" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AE6" s="3" t="s">
         <v>189</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK6" s="3" t="s">
         <v>190</v>
@@ -9468,106 +9456,106 @@
         <v>125</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>192</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>193</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH7" s="3" t="s">
         <v>194</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK7" s="3" t="s">
         <v>195</v>
@@ -9581,109 +9569,109 @@
         <v>125</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>197</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI8" s="3" t="s">
         <v>198</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
@@ -9694,109 +9682,109 @@
         <v>125</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Z9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI9" s="3" t="s">
         <v>201</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.25">
@@ -9807,64 +9795,64 @@
         <v>122</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>163</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>203</v>
@@ -9888,25 +9876,25 @@
         <v>168</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ10" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK10" s="3" t="s">
         <v>206</v>
@@ -9920,106 +9908,106 @@
         <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>171</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>172</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AE11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AG11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK11" s="3" t="s">
         <v>208</v>
@@ -10033,106 +10021,106 @@
         <v>122</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>175</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>176</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>177</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>178</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK12" s="3" t="s">
         <v>210</v>
@@ -10146,64 +10134,64 @@
         <v>122</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>181</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>176</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W13" s="3" t="s">
         <v>203</v>
@@ -10224,28 +10212,28 @@
         <v>185</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK13" s="3" t="s">
         <v>214</v>
@@ -10259,106 +10247,106 @@
         <v>122</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>188</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>172</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD14" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>216</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ14" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>217</v>
@@ -10372,106 +10360,106 @@
         <v>122</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>192</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>193</v>
       </c>
       <c r="Z15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>194</v>
       </c>
       <c r="AI15" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ15" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK15" s="3" t="s">
         <v>219</v>
@@ -10485,106 +10473,106 @@
         <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>197</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y16" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI16" s="3" t="s">
         <v>198</v>
       </c>
       <c r="AJ16" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK16" s="3" t="s">
         <v>221</v>
@@ -10598,106 +10586,106 @@
         <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AD17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>201</v>
       </c>
       <c r="AJ17" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK17" s="3" t="s">
         <v>223</v>
@@ -10724,13 +10712,13 @@
         <v>224</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10738,13 +10726,13 @@
         <v>122</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10752,13 +10740,13 @@
         <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -10766,13 +10754,13 @@
         <v>122</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10780,13 +10768,13 @@
         <v>125</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -10794,13 +10782,13 @@
         <v>125</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -10808,13 +10796,13 @@
         <v>125</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -10835,7 +10823,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>226</v>
@@ -10844,15 +10832,15 @@
         <v>168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>227</v>
@@ -10863,10 +10851,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>229</v>
@@ -10877,10 +10865,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>231</v>
@@ -10891,10 +10879,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>233</v>
@@ -10905,10 +10893,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>235</v>
@@ -10919,10 +10907,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>237</v>
@@ -10961,10 +10949,10 @@
         <v>242</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
